--- a/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:57</t>
+    <t xml:space="preserve">2026-09-10 01:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:08</t>
+    <t xml:space="preserve">2026-09-12 22:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:20</t>
+    <t xml:space="preserve">2026-09-23 23:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:49</t>
+    <t xml:space="preserve">2026-10-02 15:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Talcahuano</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:59</t>
+    <t xml:space="preserve">2026-10-04 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:28</t>
+    <t xml:space="preserve">2026-10-05 15:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
